--- a/مرافق_البصريات_للاستيراد.xlsx
+++ b/مرافق_البصريات_للاستيراد.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64997D03-E260-4AEE-AAC2-E06F0D0CECE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6391D9FD-2DC3-4D22-95B3-5A4972BA3858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>اسم المرفق</t>
   </si>
@@ -94,9 +94,6 @@
     <t>الأميرة للنظارات</t>
   </si>
   <si>
-    <t>waljahmi_eye</t>
-  </si>
-  <si>
     <t>wsati_eye</t>
   </si>
   <si>
@@ -152,6 +149,15 @@
   </si>
   <si>
     <t>wderna_eye</t>
+  </si>
+  <si>
+    <t>الجهمي للبصريات</t>
+  </si>
+  <si>
+    <t>wjahmi_eye</t>
+  </si>
+  <si>
+    <t>waljahmi_g_eye</t>
   </si>
 </sst>
 </file>
@@ -536,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -551,164 +557,172 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
